--- a/public/xlsx/예스콘 (5.xlsx
+++ b/public/xlsx/예스콘 (5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mooni\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C64E2C5-B994-4E47-B98E-6B121EDF94A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C23C1D0-D321-449A-A0A6-9A3624C84862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24375" yWindow="2520" windowWidth="21600" windowHeight="11295" tabRatio="888" firstSheet="25" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27600" yWindow="2520" windowWidth="21600" windowHeight="11295" tabRatio="888" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="에스콘" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1033">
   <si>
     <t>방.거실 벽면전체도배[270,000] , 욕실문경첩교체[30,000] , 현관센스[20,000] , 양변기 버턴교체[10,000]</t>
   </si>
@@ -363,9 +363,6 @@
     <t>강미정 대리님</t>
   </si>
   <si>
-    <t>최양숙 대리님</t>
-  </si>
-  <si>
     <t>벽면전체</t>
   </si>
   <si>
@@ -382,9 +379,6 @@
   </si>
   <si>
     <t>601호</t>
-  </si>
-  <si>
-    <t>다도해 아트빌</t>
   </si>
   <si>
     <t>장판시공</t>
@@ -1532,9 +1526,6 @@
     <t>입금(2024.10.30)</t>
   </si>
   <si>
-    <t>010-8593-0364</t>
-  </si>
-  <si>
     <t>현관문 디지털도어락교체</t>
   </si>
   <si>
@@ -1607,9 +1598,6 @@
     <t>입금(2025.1.24)</t>
   </si>
   <si>
-    <t>010-5909-0365</t>
-  </si>
-  <si>
     <t>입금(2024.11.6)</t>
   </si>
   <si>
@@ -1626,9 +1614,6 @@
   </si>
   <si>
     <t>벽 일부 도배,  장판시공</t>
-  </si>
-  <si>
-    <t>010-8280-0365</t>
   </si>
   <si>
     <t>입금(2025.2.17)</t>
@@ -1674,16 +1659,10 @@
     <t>입금(2025.5.30)</t>
   </si>
   <si>
-    <t>힐그린빌(현관:1914#)</t>
-  </si>
-  <si>
     <t>입금(2024.12.2)</t>
   </si>
   <si>
     <t>세면대 배수구 트랩 교체</t>
-  </si>
-  <si>
-    <t>010-8686-0365</t>
   </si>
   <si>
     <t>입금[2025.5.28]</t>
@@ -2423,9 +2402,6 @@
     <t>호실</t>
   </si>
   <si>
-    <t>비룡</t>
-  </si>
-  <si>
     <t>가격</t>
   </si>
   <si>
@@ -3950,6 +3926,42 @@
   </si>
   <si>
     <t>입금(2026.5.20)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>다도해 아트빌</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-8686-0365</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-8593-0364</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-8280-0365</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5909-0365</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>박과장님</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>최양숙 대리님</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>힐그린빌(현관:1914#)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>비룡</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -4138,7 +4150,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -4403,6 +4415,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4424,7 +4533,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4947,9 +5056,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5087,6 +5193,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5656,11 +5795,11 @@
     </row>
     <row r="5" spans="2:11" ht="29.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
-      <c r="C5" s="175" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="176"/>
-      <c r="E5" s="177"/>
+      <c r="C5" s="174" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="175"/>
+      <c r="E5" s="176"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -5671,7 +5810,7 @@
     <row r="6" spans="2:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10"/>
       <c r="C6" s="15" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>17</v>
@@ -5690,7 +5829,7 @@
         <v>76</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>455</v>
+        <v>1027</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="10"/>
@@ -5706,7 +5845,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>473</v>
+        <v>1025</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="10"/>
@@ -5722,7 +5861,7 @@
         <v>56</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="10"/>
@@ -5738,7 +5877,7 @@
         <v>85</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>423</v>
+        <v>1026</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="10"/>
@@ -5754,7 +5893,7 @@
         <v>80</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>448</v>
+        <v>1028</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="10"/>
@@ -5767,10 +5906,10 @@
     <row r="12" spans="2:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="10"/>
       <c r="C12" s="15" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="10"/>
@@ -5783,10 +5922,10 @@
     <row r="13" spans="2:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10"/>
       <c r="C13" s="18" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="D13" s="145" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="10"/>
@@ -5823,11 +5962,11 @@
       <c r="B16" s="10">
         <v>1</v>
       </c>
-      <c r="C16" s="174" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>100</v>
+      <c r="C16" s="220" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D16" s="221" t="s">
+        <v>1024</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -5840,8 +5979,8 @@
       <c r="B17" s="10">
         <v>2</v>
       </c>
-      <c r="C17" s="174"/>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="222"/>
+      <c r="D17" s="223" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="10"/>
@@ -5853,8 +5992,8 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="10"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="222"/>
+      <c r="D18" s="223"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -5864,8 +6003,8 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="10"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="222"/>
+      <c r="D19" s="223" t="s">
         <v>89</v>
       </c>
       <c r="F19" s="10"/>
@@ -5877,8 +6016,8 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="10"/>
-      <c r="C20" s="174"/>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="222"/>
+      <c r="D20" s="223" t="s">
         <v>50</v>
       </c>
       <c r="F20" s="10"/>
@@ -5890,8 +6029,8 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
-      <c r="C21" s="174"/>
-      <c r="D21" s="10"/>
+      <c r="C21" s="224"/>
+      <c r="D21" s="225"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -5914,14 +6053,14 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="10"/>
-      <c r="C23" s="174" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
+      <c r="C23" s="220" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D23" s="226" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E23" s="226"/>
+      <c r="F23" s="221"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
@@ -5930,12 +6069,12 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="10"/>
-      <c r="C24" s="174"/>
-      <c r="D24" s="10" t="s">
-        <v>656</v>
-      </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+      <c r="C24" s="222"/>
+      <c r="D24" s="227" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E24" s="227"/>
+      <c r="F24" s="223"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
@@ -5944,12 +6083,12 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="10"/>
-      <c r="C25" s="174"/>
-      <c r="D25" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
+      <c r="C25" s="222"/>
+      <c r="D25" s="227" t="s">
+        <v>544</v>
+      </c>
+      <c r="E25" s="227"/>
+      <c r="F25" s="223"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
@@ -5958,12 +6097,12 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="10"/>
-      <c r="C26" s="174"/>
-      <c r="D26" s="10" t="s">
-        <v>640</v>
-      </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+      <c r="C26" s="222"/>
+      <c r="D26" s="227" t="s">
+        <v>633</v>
+      </c>
+      <c r="E26" s="227"/>
+      <c r="F26" s="223"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
@@ -5972,15 +6111,15 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="10"/>
-      <c r="C27" s="174"/>
-      <c r="D27" s="10" t="s">
-        <v>897</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>899</v>
+      <c r="C27" s="222"/>
+      <c r="D27" s="227" t="s">
+        <v>889</v>
+      </c>
+      <c r="E27" s="227" t="s">
+        <v>890</v>
+      </c>
+      <c r="F27" s="223" t="s">
+        <v>891</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -5990,15 +6129,15 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
-      <c r="C28" s="174"/>
-      <c r="D28" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>896</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>899</v>
+      <c r="C28" s="222"/>
+      <c r="D28" s="227" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="227" t="s">
+        <v>888</v>
+      </c>
+      <c r="F28" s="223" t="s">
+        <v>891</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
@@ -6008,12 +6147,12 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="10"/>
-      <c r="C29" s="174"/>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="222"/>
+      <c r="D29" s="227" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+      <c r="E29" s="227"/>
+      <c r="F29" s="223"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
@@ -6022,13 +6161,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="10"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="10" t="s">
-        <v>900</v>
-      </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10" t="s">
-        <v>901</v>
+      <c r="C30" s="222"/>
+      <c r="D30" s="227" t="s">
+        <v>892</v>
+      </c>
+      <c r="E30" s="227"/>
+      <c r="F30" s="223" t="s">
+        <v>893</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -6038,18 +6177,18 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="10"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="10" t="s">
-        <v>902</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>903</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>904</v>
+      <c r="C31" s="222"/>
+      <c r="D31" s="227" t="s">
+        <v>894</v>
+      </c>
+      <c r="E31" s="227" t="s">
+        <v>895</v>
+      </c>
+      <c r="F31" s="223" t="s">
+        <v>896</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
@@ -6058,12 +6197,12 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="10"/>
-      <c r="C32" s="174"/>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="222"/>
+      <c r="D32" s="227" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+      <c r="E32" s="227"/>
+      <c r="F32" s="223"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -6072,12 +6211,12 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="10"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
+      <c r="C33" s="222"/>
+      <c r="D33" s="227" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33" s="227"/>
+      <c r="F33" s="223"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
@@ -6086,12 +6225,12 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="10"/>
-      <c r="C34" s="174"/>
-      <c r="D34" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="228" t="s">
+        <v>839</v>
+      </c>
+      <c r="E34" s="228"/>
+      <c r="F34" s="225"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -6112,11 +6251,11 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="10"/>
-      <c r="C36" s="174" t="s">
+      <c r="C36" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>205</v>
+      <c r="D36" s="221" t="s">
+        <v>203</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -6128,8 +6267,8 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="10"/>
-      <c r="C37" s="174"/>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="222"/>
+      <c r="D37" s="223" t="s">
         <v>43</v>
       </c>
       <c r="E37" s="10"/>
@@ -6142,8 +6281,8 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="10"/>
-      <c r="C38" s="174"/>
-      <c r="D38" s="10" t="s">
+      <c r="C38" s="222"/>
+      <c r="D38" s="223" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="10"/>
@@ -6156,9 +6295,9 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="10"/>
-      <c r="C39" s="174"/>
-      <c r="D39" s="10" t="s">
-        <v>111</v>
+      <c r="C39" s="222"/>
+      <c r="D39" s="223" t="s">
+        <v>109</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -6170,9 +6309,9 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="10"/>
-      <c r="C40" s="174"/>
-      <c r="D40" s="10" t="s">
-        <v>127</v>
+      <c r="C40" s="222"/>
+      <c r="D40" s="223" t="s">
+        <v>125</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -6184,9 +6323,9 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="10"/>
-      <c r="C41" s="174"/>
-      <c r="D41" s="10" t="s">
-        <v>195</v>
+      <c r="C41" s="222"/>
+      <c r="D41" s="223" t="s">
+        <v>193</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -6198,8 +6337,8 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
-      <c r="C42" s="174"/>
-      <c r="D42" s="10" t="s">
+      <c r="C42" s="222"/>
+      <c r="D42" s="223" t="s">
         <v>84</v>
       </c>
       <c r="E42" s="10"/>
@@ -6212,9 +6351,9 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="10"/>
-      <c r="C43" s="174"/>
-      <c r="D43" s="10" t="s">
-        <v>131</v>
+      <c r="C43" s="224"/>
+      <c r="D43" s="225" t="s">
+        <v>129</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
@@ -6238,16 +6377,16 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="10"/>
-      <c r="C45" s="174" t="s">
+      <c r="C45" s="220" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="226" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="F45" s="10"/>
+      <c r="E45" s="226" t="s">
+        <v>884</v>
+      </c>
+      <c r="F45" s="221"/>
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
@@ -6256,15 +6395,15 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="10"/>
-      <c r="C46" s="174"/>
-      <c r="D46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>888</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>889</v>
+      <c r="C46" s="222"/>
+      <c r="D46" s="227" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="227" t="s">
+        <v>880</v>
+      </c>
+      <c r="F46" s="223" t="s">
+        <v>881</v>
       </c>
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
@@ -6274,14 +6413,14 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="10"/>
-      <c r="C47" s="174"/>
-      <c r="D47" s="10" t="s">
-        <v>890</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>891</v>
-      </c>
-      <c r="F47" s="10"/>
+      <c r="C47" s="222"/>
+      <c r="D47" s="227" t="s">
+        <v>882</v>
+      </c>
+      <c r="E47" s="227" t="s">
+        <v>883</v>
+      </c>
+      <c r="F47" s="223"/>
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
@@ -6290,15 +6429,15 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="10"/>
-      <c r="C48" s="174"/>
-      <c r="D48" s="10" t="s">
-        <v>893</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>894</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>895</v>
+      <c r="C48" s="222"/>
+      <c r="D48" s="227" t="s">
+        <v>885</v>
+      </c>
+      <c r="E48" s="227" t="s">
+        <v>886</v>
+      </c>
+      <c r="F48" s="223" t="s">
+        <v>887</v>
       </c>
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
@@ -6308,12 +6447,12 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="10"/>
-      <c r="C49" s="174"/>
-      <c r="D49" s="10" t="s">
-        <v>848</v>
-      </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
+      <c r="C49" s="224"/>
+      <c r="D49" s="228" t="s">
+        <v>840</v>
+      </c>
+      <c r="E49" s="228"/>
+      <c r="F49" s="225"/>
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
@@ -6322,12 +6461,6 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="10"/>
-      <c r="C50" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
@@ -6338,8 +6471,12 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="10"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="10"/>
+      <c r="C51" s="229" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="230" t="s">
+        <v>168</v>
+      </c>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
       <c r="G51" s="10"/>
@@ -8628,20 +8765,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -8658,10 +8795,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -8669,20 +8806,20 @@
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="F3" s="64">
         <v>140000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="H3" s="62"/>
       <c r="K3" s="84" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L3" s="84">
         <v>25000</v>
@@ -8691,25 +8828,25 @@
     <row r="4" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="24"/>
       <c r="C4" s="62" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="F4" s="42">
         <v>60000</v>
       </c>
       <c r="G4" s="88" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="H4" s="60" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="K4" s="84" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L4" s="84">
         <v>40000</v>
@@ -10115,10 +10252,10 @@
         <v>61</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>26</v>
@@ -10159,16 +10296,16 @@
         <v>20</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I2" s="2">
         <v>500000</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -10294,20 +10431,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>389</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -10324,10 +10461,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -10337,20 +10474,20 @@
         <v>63</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F3" s="2">
         <v>40000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H3" s="3"/>
       <c r="K3" s="84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L3" s="84">
         <v>40000</v>
@@ -10361,23 +10498,23 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="E4" s="69" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="F4" s="22">
         <v>110000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H4" s="25"/>
       <c r="K4" s="84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L4" s="84">
         <v>40000</v>
@@ -10391,20 +10528,20 @@
         <v>88</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F5" s="22">
         <v>150000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H5" s="25"/>
       <c r="K5" s="84" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L5" s="84">
         <v>150000</v>
@@ -10415,19 +10552,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F6" s="22">
         <v>40000</v>
       </c>
       <c r="G6" s="70" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -10439,16 +10576,16 @@
         <v>71</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="F7" s="54">
         <v>40000</v>
       </c>
       <c r="G7" s="70" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -10457,11 +10594,11 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="46" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F8" s="54"/>
       <c r="G8" s="71"/>
@@ -10472,10 +10609,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E9" s="45" t="s">
         <v>31</v>
@@ -10484,7 +10621,7 @@
         <v>400000</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -10493,10 +10630,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E10" s="45" t="s">
         <v>11</v>
@@ -10514,19 +10651,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="F11" s="54">
         <v>44000</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="H11" s="25"/>
     </row>
@@ -10535,17 +10672,17 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="45" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="F12" s="53">
         <v>79000</v>
       </c>
       <c r="G12" s="128" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="H12" s="25"/>
     </row>
@@ -10554,11 +10691,11 @@
         <v>11</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="45" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="F13" s="53"/>
       <c r="G13" s="24"/>
@@ -11876,20 +12013,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>606</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>599</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -11906,10 +12043,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -11919,16 +12056,16 @@
         <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="F3" s="2">
         <v>80000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -13334,20 +13471,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -13364,10 +13501,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -13377,16 +13514,16 @@
         <v>83</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F3" s="2">
         <v>150000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -13395,19 +13532,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E4" s="69" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F4" s="22">
         <v>15000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -13419,16 +13556,16 @@
         <v>71</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="F5" s="22">
         <v>130000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -13440,16 +13577,16 @@
         <v>81</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="F6" s="22">
         <v>80000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -13458,19 +13595,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="F7" s="54">
         <v>50000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -13482,10 +13619,10 @@
         <v>71</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="F8" s="54">
         <v>77000</v>
@@ -13500,19 +13637,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="F9" s="54">
         <v>44000</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -13521,19 +13658,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="F10" s="54">
         <v>50000</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="H10" s="25"/>
     </row>
@@ -13542,19 +13679,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="F11" s="54">
         <v>30000</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="H11" s="25"/>
     </row>
@@ -13563,20 +13700,20 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="F12" s="53">
         <v>77000</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="153" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -14900,20 +15037,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>387</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -14930,10 +15067,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -14941,10 +15078,10 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="F3" s="2">
         <v>30000</v>
@@ -14959,19 +15096,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E4" s="69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F4" s="22">
         <v>120000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -16377,10 +16514,10 @@
         <v>61</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="G1" s="32" t="s">
         <v>26</v>
@@ -16409,22 +16546,22 @@
         <v>87</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J2" s="2">
         <v>90000</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -16550,20 +16687,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>546</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>539</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -16581,7 +16718,7 @@
         <v>22</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -16592,20 +16729,20 @@
         <v>55</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F3" s="79">
         <v>30000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H3" s="3"/>
       <c r="K3" s="106" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L3" s="65">
         <v>190000</v>
@@ -16616,25 +16753,25 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F4" s="65">
         <v>370000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K4" s="106" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L4" s="65">
         <v>40000</v>
@@ -16645,23 +16782,23 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="F5" s="53">
         <v>430000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="H5" s="25"/>
       <c r="K5" s="106" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L5" s="65">
         <v>30000</v>
@@ -16675,20 +16812,20 @@
         <v>71</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F6" s="54">
         <v>90000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="82" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L6" s="65">
         <v>300000</v>
@@ -16699,23 +16836,23 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F7" s="54">
         <v>40000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H7" s="25"/>
       <c r="K7" s="106" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L7" s="65">
         <v>40000</v>
@@ -16729,20 +16866,20 @@
         <v>62</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F8" s="54">
         <v>190000</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H8" s="25"/>
       <c r="K8" s="106" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L8" s="65">
         <v>50000</v>
@@ -16756,7 +16893,7 @@
         <v>70</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>2</v>
@@ -16765,11 +16902,11 @@
         <v>765000</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H9" s="25"/>
       <c r="K9" s="106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L9" s="65">
         <v>70000</v>
@@ -16780,19 +16917,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="F10" s="54">
         <v>30000</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="H10" s="25"/>
       <c r="K10" s="106" t="s">
@@ -16807,23 +16944,23 @@
         <v>9</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="F11" s="54">
         <v>177000</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="H11" s="25"/>
       <c r="K11" s="106" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L11" s="65">
         <v>35000</v>
@@ -16834,19 +16971,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="D12" s="24">
         <v>2026.4</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="F12" s="54">
         <v>44000</v>
       </c>
-      <c r="G12" s="211" t="s">
-        <v>912</v>
+      <c r="G12" s="210" t="s">
+        <v>904</v>
       </c>
       <c r="H12" s="25"/>
       <c r="K12" s="106"/>
@@ -16856,18 +16993,18 @@
         <v>11</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="D13" s="24">
         <v>2026.4</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="F13" s="54">
         <v>29700</v>
       </c>
-      <c r="G13" s="204"/>
+      <c r="G13" s="203"/>
       <c r="H13" s="25"/>
       <c r="K13" s="106"/>
     </row>
@@ -16876,18 +17013,18 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="D14" s="24">
         <v>2026.4</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="F14" s="54">
         <v>29700</v>
       </c>
-      <c r="G14" s="204"/>
+      <c r="G14" s="203"/>
       <c r="H14" s="25"/>
       <c r="K14" s="106"/>
     </row>
@@ -16896,18 +17033,18 @@
         <v>13</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D15" s="24">
         <v>2026.4</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="F15" s="54">
         <v>20000</v>
       </c>
-      <c r="G15" s="212"/>
+      <c r="G15" s="211"/>
       <c r="H15" s="25"/>
       <c r="K15" s="106"/>
     </row>
@@ -16916,23 +17053,23 @@
         <v>14</v>
       </c>
       <c r="C16" s="161" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="D16" s="161" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="E16" s="162" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="F16" s="163">
         <v>115500</v>
       </c>
       <c r="G16" s="161" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="H16" s="25"/>
       <c r="K16" s="106" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L16" s="65">
         <v>15000</v>
@@ -16943,23 +17080,23 @@
         <v>15</v>
       </c>
       <c r="C17" s="161" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="D17" s="161" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="E17" s="162" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="F17" s="164">
         <v>143000</v>
       </c>
       <c r="G17" s="161" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="H17" s="25"/>
       <c r="K17" s="106" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L17" s="65">
         <v>40000</v>
@@ -16970,17 +17107,17 @@
         <v>16</v>
       </c>
       <c r="C18" s="161" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="D18" s="165"/>
       <c r="E18" s="162" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="F18" s="163"/>
       <c r="G18" s="165"/>
       <c r="H18" s="25"/>
       <c r="K18" s="106" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L18" s="65">
         <v>20000</v>
@@ -16991,25 +17128,25 @@
         <v>17</v>
       </c>
       <c r="C19" s="154" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="D19" s="154">
         <v>2026.5</v>
       </c>
       <c r="E19" s="155" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="F19" s="166">
         <v>60000</v>
       </c>
       <c r="G19" s="154" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="K19" s="106" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L19" s="65">
         <v>40000</v>
@@ -17020,25 +17157,25 @@
         <v>18</v>
       </c>
       <c r="C20" s="154" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="D20" s="154">
         <v>2026.5</v>
       </c>
       <c r="E20" s="155" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="F20" s="166">
         <v>189700</v>
       </c>
       <c r="G20" s="154" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="K20" s="106" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L20" s="65">
         <v>30000</v>
@@ -17049,25 +17186,25 @@
         <v>19</v>
       </c>
       <c r="C21" s="154" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="D21" s="154">
         <v>2026.5</v>
       </c>
       <c r="E21" s="155" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="F21" s="166">
         <v>79000</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="K21" s="106" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L21" s="65">
         <v>15000</v>
@@ -17078,22 +17215,22 @@
         <v>20</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="F22" s="160">
         <v>71500</v>
       </c>
       <c r="G22" s="135" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -17230,20 +17367,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>706</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>698</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -17261,7 +17398,7 @@
         <v>22</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -17273,19 +17410,19 @@
         <v>2024</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F3" s="79">
         <v>50000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L3" s="65">
         <v>50000</v>
@@ -17299,20 +17436,20 @@
         <v>60</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F4" s="65">
         <v>225000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H4" s="25"/>
       <c r="K4" s="10" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="L4" s="65">
         <v>80000</v>
@@ -17326,20 +17463,20 @@
         <v>44</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="F5" s="53">
         <v>100000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H5" s="25"/>
       <c r="K5" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L5" s="65">
         <v>50000</v>
@@ -17362,11 +17499,11 @@
         <v>845000</v>
       </c>
       <c r="G6" s="103" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L6" s="65">
         <v>20000</v>
@@ -17383,17 +17520,17 @@
         <v>2025.4</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="F7" s="54">
         <v>155000</v>
       </c>
-      <c r="G7" s="186" t="s">
-        <v>489</v>
+      <c r="G7" s="185" t="s">
+        <v>482</v>
       </c>
       <c r="H7" s="25"/>
       <c r="K7" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L7" s="65">
         <v>35000</v>
@@ -17404,21 +17541,21 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D8" s="24">
         <v>2025.4</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="F8" s="54">
         <v>75000</v>
       </c>
-      <c r="G8" s="187"/>
+      <c r="G8" s="186"/>
       <c r="H8" s="25"/>
       <c r="K8" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L8" s="65">
         <v>20000</v>
@@ -17432,20 +17569,20 @@
         <v>51</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="F9" s="54">
         <v>200000</v>
       </c>
       <c r="G9" s="102" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="H9" s="25"/>
       <c r="K9" s="10" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="L9" s="65">
         <v>50000</v>
@@ -17456,23 +17593,23 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F10" s="54">
         <v>65000</v>
       </c>
       <c r="G10" s="102" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="H10" s="25"/>
       <c r="K10" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L10" s="65">
         <v>100000</v>
@@ -17486,20 +17623,20 @@
         <v>44</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="F11" s="54">
         <v>290000</v>
       </c>
       <c r="G11" s="102" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H11" s="25"/>
       <c r="K11" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L11" s="65">
         <v>15000</v>
@@ -17510,23 +17647,23 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F12" s="53">
         <v>80000</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H12" s="25"/>
       <c r="K12" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L12" s="65">
         <v>30000</v>
@@ -17537,23 +17674,23 @@
         <v>11</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="F13" s="53">
         <v>90000</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H13" s="25"/>
       <c r="K13" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L13" s="65">
         <v>30000</v>
@@ -17564,23 +17701,23 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F14" s="53">
         <v>80000</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H14" s="25"/>
       <c r="K14" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L14" s="65">
         <v>20000</v>
@@ -17591,22 +17728,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F15" s="65">
         <v>50000</v>
       </c>
       <c r="G15" s="111" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L15" s="65">
         <v>50000</v>
@@ -17617,22 +17754,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F16" s="65">
         <v>60000</v>
       </c>
       <c r="G16" s="111" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L16" s="65">
         <v>20000</v>
@@ -17646,19 +17783,19 @@
         <v>60</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F17" s="65">
         <v>40000</v>
       </c>
       <c r="G17" s="111" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L17" s="65">
         <v>20000</v>
@@ -17672,19 +17809,19 @@
         <v>21</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="F18" s="65">
         <v>69000</v>
       </c>
       <c r="G18" s="111" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L18" s="65">
         <v>35000</v>
@@ -17698,19 +17835,19 @@
         <v>44</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F19" s="65">
         <v>355000</v>
       </c>
       <c r="G19" s="111" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L19" s="65">
         <v>50000</v>
@@ -17721,7 +17858,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D20" s="12">
         <v>2025</v>
@@ -17733,10 +17870,10 @@
         <v>370000</v>
       </c>
       <c r="G20" s="111" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L20" s="65">
         <v>30000</v>
@@ -17747,22 +17884,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="D21" s="12">
         <v>2026.5</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="F21" s="65">
         <v>275000</v>
       </c>
       <c r="G21" s="150" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -17877,20 +18014,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>385</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>383</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -17907,10 +18044,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -17920,16 +18057,16 @@
         <v>68</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="F3" s="64">
         <v>110000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -17938,10 +18075,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E4" s="41" t="s">
         <v>12</v>
@@ -17950,7 +18087,7 @@
         <v>135000</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -17962,16 +18099,16 @@
         <v>83</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="F5" s="53">
         <v>40000</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -17980,19 +18117,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F6" s="22">
         <v>100000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -18001,19 +18138,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F7" s="22">
         <v>70000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -18022,19 +18159,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="F8" s="22">
         <v>136000</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -18043,19 +18180,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="E9" s="137" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="F9" s="22">
         <v>294000</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -18286,20 +18423,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>209</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="109"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="123" t="s">
         <v>86</v>
@@ -18316,10 +18453,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="179" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="179"/>
+      <c r="K2" s="178" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="178"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -18334,11 +18471,11 @@
         <v>694000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="H3" s="10"/>
       <c r="K3" s="82" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L3" s="84">
         <v>50000</v>
@@ -18357,11 +18494,11 @@
         <v>372000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H4" s="25"/>
       <c r="K4" s="82" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="L4" s="84">
         <v>25000</v>
@@ -18372,21 +18509,21 @@
         <v>3</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D5" s="125"/>
       <c r="E5" s="45" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="F5" s="54">
         <v>150000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H5" s="25"/>
       <c r="K5" s="82" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L5" s="84">
         <v>35000</v>
@@ -18407,11 +18544,11 @@
         <v>140000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="82" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L6" s="84">
         <v>30000</v>
@@ -18425,20 +18562,20 @@
         <v>65</v>
       </c>
       <c r="D7" s="125" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="F7" s="54">
         <v>90000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="H7" s="25"/>
       <c r="K7" s="82" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="L7" s="84">
         <v>40000</v>
@@ -18453,16 +18590,16 @@
       </c>
       <c r="D8" s="125"/>
       <c r="E8" s="46" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F8" s="54">
         <v>530000</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K8" s="82" t="s">
         <v>67</v>
@@ -18479,22 +18616,22 @@
         <v>51</v>
       </c>
       <c r="D9" s="125" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F9" s="54">
         <v>170000</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L9" s="84">
         <v>100000</v>
@@ -18508,20 +18645,20 @@
         <v>73</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F10" s="54">
         <v>195000</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H10" s="25"/>
       <c r="K10" s="82" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L10" s="84">
         <v>45000</v>
@@ -18535,20 +18672,20 @@
         <v>70</v>
       </c>
       <c r="D11" s="125" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="F11" s="54">
         <v>749000</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H11" s="25"/>
       <c r="K11" s="82" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L11" s="84">
         <v>10000</v>
@@ -18562,20 +18699,20 @@
         <v>81</v>
       </c>
       <c r="D12" s="125" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="F12" s="53">
         <v>130000</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H12" s="25"/>
       <c r="K12" s="82" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L12" s="84">
         <v>35000</v>
@@ -18589,20 +18726,20 @@
         <v>60</v>
       </c>
       <c r="D13" s="125" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="F13" s="53">
         <v>125000</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H13" s="25"/>
       <c r="K13" s="82" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="L13" s="84">
         <v>20000</v>
@@ -18617,17 +18754,17 @@
       </c>
       <c r="D14" s="125"/>
       <c r="E14" s="45" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F14" s="53">
         <v>50000</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H14" s="25"/>
       <c r="K14" s="82" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L14" s="84">
         <v>24000</v>
@@ -18641,20 +18778,20 @@
         <v>60</v>
       </c>
       <c r="D15" s="125" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F15" s="53">
         <v>50000</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H15" s="25"/>
       <c r="K15" s="82" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L15" s="84">
         <v>15000</v>
@@ -18668,20 +18805,20 @@
         <v>46</v>
       </c>
       <c r="D16" s="125" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="F16" s="53">
         <v>550000</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="H16" s="25"/>
       <c r="K16" s="82" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L16" s="84">
         <v>20000</v>
@@ -18695,20 +18832,20 @@
         <v>79</v>
       </c>
       <c r="D17" s="125" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="F17" s="53">
         <v>230000</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H17" s="25"/>
       <c r="K17" s="82" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L17" s="84">
         <v>30000</v>
@@ -18719,23 +18856,23 @@
         <v>16</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D18" s="125" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F18" s="53">
         <v>33000</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="H18" s="25"/>
       <c r="K18" s="82" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L18" s="84">
         <v>100000</v>
@@ -18746,23 +18883,23 @@
         <v>17</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="D19" s="125" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="F19" s="53">
         <v>330000</v>
       </c>
       <c r="G19" s="128" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="H19" s="25"/>
       <c r="K19" s="82" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L19" s="84">
         <v>70000</v>
@@ -18773,23 +18910,23 @@
         <v>18</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="F20" s="53">
         <v>135000</v>
       </c>
       <c r="G20" s="128" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="H20" s="34"/>
       <c r="K20" s="82" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L20" s="84">
         <v>20000</v>
@@ -18804,7 +18941,7 @@
       <c r="G21" s="25"/>
       <c r="H21" s="34"/>
       <c r="K21" s="82" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L21" s="84">
         <v>70000</v>
@@ -18819,7 +18956,7 @@
       <c r="G22" s="25"/>
       <c r="H22" s="34"/>
       <c r="K22" s="82" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="L22" s="84">
         <v>45000</v>
@@ -18864,7 +19001,7 @@
       <c r="G25" s="25"/>
       <c r="H25" s="34"/>
       <c r="K25" s="82" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="L25" s="84">
         <v>55000</v>
@@ -18879,13 +19016,13 @@
       <c r="G26" s="25"/>
       <c r="H26" s="34"/>
       <c r="K26" s="82" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="L26" s="148">
         <v>75000</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -18897,13 +19034,13 @@
       <c r="G27" s="25"/>
       <c r="H27" s="34"/>
       <c r="K27" s="82" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="L27" s="148">
         <v>60000</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -19012,20 +19149,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>390</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -19042,10 +19179,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -19055,16 +19192,16 @@
         <v>44</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="F3" s="64">
         <v>50000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -19073,19 +19210,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="F4" s="42">
         <v>150000</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -19360,20 +19497,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>388</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -19390,20 +19527,20 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>6</v>
@@ -19412,11 +19549,11 @@
         <v>1100000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H3" s="3"/>
       <c r="K3" s="84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L3" s="84">
         <v>200000</v>
@@ -19427,23 +19564,23 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="F4" s="42">
         <v>100000</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H4" s="25"/>
       <c r="K4" s="84" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L4" s="84">
         <v>250000</v>
@@ -19454,19 +19591,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="F5" s="42">
         <v>500000</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -19478,16 +19615,16 @@
         <v>51</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="F6" s="22">
         <v>250000</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -19496,19 +19633,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F7" s="22">
         <v>530000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -19527,7 +19664,7 @@
         <v>495000</v>
       </c>
       <c r="G8" s="128" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -19767,7 +19904,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -19779,7 +19916,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -19796,10 +19933,10 @@
       <c r="H2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -19809,16 +19946,16 @@
         <v>46</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="F3" s="64">
         <v>485000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -19827,22 +19964,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F4" s="42">
         <v>100000</v>
       </c>
-      <c r="G4" s="194" t="s">
-        <v>464</v>
+      <c r="G4" s="193" t="s">
+        <v>459</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -19853,17 +19990,17 @@
         <v>55</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F5" s="53">
         <v>170000</v>
       </c>
-      <c r="G5" s="202"/>
+      <c r="G5" s="201"/>
       <c r="H5" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -19874,16 +20011,16 @@
         <v>60</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F6" s="54">
         <v>35000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -19895,16 +20032,16 @@
         <v>71</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="F7" s="54">
         <v>60000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -19913,19 +20050,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F8" s="54">
         <v>66000</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -19934,20 +20071,20 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="F9" s="54">
         <v>50000</v>
       </c>
       <c r="G9" s="24"/>
       <c r="H9" s="25" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -20178,7 +20315,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -20190,7 +20327,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -20207,10 +20344,10 @@
       <c r="H2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -20218,16 +20355,16 @@
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="3" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="F3" s="2">
         <v>396000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -20512,7 +20649,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -20524,7 +20661,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -20541,10 +20678,10 @@
       <c r="H2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="179" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="179"/>
+      <c r="K2" s="178" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="178"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -20554,20 +20691,20 @@
         <v>69</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F3" s="73">
         <v>120000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="H3" s="3"/>
       <c r="K3" s="82" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L3" s="83">
         <v>120000</v>
@@ -20578,10 +20715,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E4" s="41" t="s">
         <v>16</v>
@@ -20590,7 +20727,7 @@
         <v>120000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H4" s="25"/>
       <c r="K4" s="82" t="s">
@@ -20608,20 +20745,20 @@
         <v>79</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="F5" s="53">
         <v>690000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H5" s="25"/>
       <c r="K5" s="82" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L5" s="83">
         <v>100000</v>
@@ -20632,10 +20769,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>36</v>
@@ -20644,11 +20781,11 @@
         <v>170000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="82" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L6" s="83">
         <v>230000</v>
@@ -20663,7 +20800,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="25"/>
       <c r="K7" s="82" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L7" s="83">
         <v>170000</v>
@@ -20899,7 +21036,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -20911,7 +21048,7 @@
     <row r="2" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -20928,10 +21065,10 @@
       <c r="H2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="1:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -20941,20 +21078,20 @@
         <v>70</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="F3" s="213">
+        <v>243</v>
+      </c>
+      <c r="F3" s="212">
         <v>110000</v>
       </c>
-      <c r="G3" s="194" t="s">
-        <v>412</v>
+      <c r="G3" s="193" t="s">
+        <v>410</v>
       </c>
       <c r="H3" s="62"/>
       <c r="K3" s="84" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L3" s="42">
         <v>190000</v>
@@ -20968,16 +21105,16 @@
         <v>79</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="185"/>
-      <c r="G4" s="202"/>
+        <v>141</v>
+      </c>
+      <c r="F4" s="184"/>
+      <c r="G4" s="201"/>
       <c r="H4" s="60"/>
       <c r="K4" s="84" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L4" s="42">
         <v>100000</v>
@@ -20991,7 +21128,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E5" s="68" t="s">
         <v>5</v>
@@ -21000,11 +21137,11 @@
         <v>635000</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H5" s="25"/>
       <c r="K5" s="84" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L5" s="42">
         <v>250000</v>
@@ -21018,7 +21155,7 @@
         <v>65</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>32</v>
@@ -21027,11 +21164,11 @@
         <v>270000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="84" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="L6" s="42">
         <v>90000</v>
@@ -21042,23 +21179,23 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="F7" s="54">
         <v>165000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="H7" s="25"/>
       <c r="K7" s="84" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L7" s="42">
         <v>40000</v>
@@ -21069,23 +21206,23 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="F8" s="54">
         <v>269700</v>
       </c>
       <c r="G8" s="128" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="H8" s="25"/>
       <c r="K8" s="84" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L8" s="42">
         <v>20000</v>
@@ -21096,7 +21233,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="45"/>
@@ -21104,7 +21241,7 @@
       <c r="G9" s="24"/>
       <c r="H9" s="25"/>
       <c r="K9" s="84" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L9" s="42">
         <v>20000</v>
@@ -21120,7 +21257,7 @@
       <c r="G10" s="24"/>
       <c r="H10" s="25"/>
       <c r="K10" s="84" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L10" s="42">
         <v>30000</v>
@@ -21135,7 +21272,7 @@
       <c r="G11" s="24"/>
       <c r="H11" s="25"/>
       <c r="K11" s="84" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L11" s="42">
         <v>35000</v>
@@ -21150,7 +21287,7 @@
       <c r="G12" s="24"/>
       <c r="H12" s="25"/>
       <c r="K12" s="107" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="L12" s="42">
         <v>30000</v>
@@ -21165,7 +21302,7 @@
       <c r="G13" s="24"/>
       <c r="H13" s="25"/>
       <c r="K13" s="84" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="L13" s="42">
         <v>40000</v>
@@ -21346,7 +21483,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -21358,7 +21495,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -21383,7 +21520,7 @@
       <c r="C3" s="61"/>
       <c r="D3" s="62"/>
       <c r="E3" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F3" s="64"/>
       <c r="G3" s="75"/>
@@ -21669,7 +21806,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -21681,7 +21818,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -21698,31 +21835,31 @@
       <c r="H2" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="214" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="214"/>
+      <c r="K2" s="213" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="213"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="8" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="F3" s="2">
         <v>40000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="H3" s="93"/>
       <c r="K3" s="90" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L3" s="91">
         <v>140000</v>
@@ -21736,20 +21873,20 @@
         <v>70</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="E4" s="95" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="F4" s="22">
         <v>207000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H4" s="85"/>
       <c r="K4" s="90" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L4" s="91">
         <v>20000</v>
@@ -21763,7 +21900,7 @@
         <v>81</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="E5" s="110" t="s">
         <v>39</v>
@@ -21772,11 +21909,11 @@
         <v>180000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H5" s="85"/>
       <c r="K5" s="90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L5" s="91">
         <v>12000</v>
@@ -21790,7 +21927,7 @@
         <v>81</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>15</v>
@@ -21799,11 +21936,11 @@
         <v>65000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H6" s="85"/>
       <c r="K6" s="90" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L6" s="91">
         <v>35000</v>
@@ -21814,19 +21951,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="F7" s="54">
         <v>29700</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="H7" s="85"/>
       <c r="L7" s="91"/>
@@ -22110,7 +22247,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -22122,7 +22259,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -22140,7 +22277,7 @@
         <v>22</v>
       </c>
       <c r="K2" s="168" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="L2" s="168"/>
     </row>
@@ -22152,20 +22289,20 @@
         <v>70</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F3" s="79">
         <v>50000</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H3" s="62"/>
       <c r="K3" s="84" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L3" s="84">
         <v>50000</v>
@@ -22176,23 +22313,23 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="F4" s="65">
         <v>130000</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="H4" s="60"/>
       <c r="K4" s="84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L4" s="84">
         <v>10000</v>
@@ -22209,19 +22346,19 @@
         <v>58</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="F5" s="53">
         <v>410000</v>
       </c>
       <c r="G5" s="169" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K5" s="84" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L5" s="84">
         <v>25000</v>
@@ -22232,23 +22369,23 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F6" s="54">
         <v>50000</v>
       </c>
       <c r="G6" s="170"/>
       <c r="H6" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K6" s="84" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="L6" s="84">
         <v>45000</v>
@@ -22259,23 +22396,23 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F7" s="54">
         <v>158000</v>
       </c>
       <c r="G7" s="171"/>
       <c r="H7" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K7" s="84" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L7" s="84">
         <v>50000</v>
@@ -22289,20 +22426,20 @@
         <v>91</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="F8" s="54">
         <v>155000</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="H8" s="25"/>
       <c r="K8" s="84" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L8" s="84">
         <v>20000</v>
@@ -22313,19 +22450,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F9" s="54">
         <v>210000</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -22334,13 +22471,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="F10" s="54">
         <v>35000</v>
@@ -22358,7 +22495,7 @@
         <v>65</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="E11" s="45" t="s">
         <v>38</v>
@@ -22367,7 +22504,7 @@
         <v>95000</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H11" s="25"/>
     </row>
@@ -22379,7 +22516,7 @@
         <v>91</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="E12" s="45" t="s">
         <v>37</v>
@@ -22388,7 +22525,7 @@
         <v>90000</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="H12" s="25"/>
     </row>
@@ -22400,7 +22537,7 @@
         <v>81</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E13" s="45" t="s">
         <v>8</v>
@@ -22409,7 +22546,7 @@
         <v>85000</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="H13" s="25"/>
     </row>
@@ -22418,19 +22555,19 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="F14" s="53">
         <v>33000</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="H14" s="25"/>
     </row>
@@ -22439,22 +22576,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="F15" s="65">
         <v>264000</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22462,22 +22599,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F16" s="65">
         <v>346500</v>
       </c>
       <c r="G16" s="172" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22485,20 +22622,20 @@
         <v>15</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="F17" s="65">
         <v>20000</v>
       </c>
       <c r="G17" s="173"/>
       <c r="H17" s="10" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22506,20 +22643,20 @@
         <v>16</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>789</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>797</v>
-      </c>
       <c r="E18" s="47" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="F18" s="65">
         <v>33000</v>
       </c>
       <c r="G18" s="173"/>
       <c r="H18" s="47" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22527,22 +22664,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="156" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="D19" s="156" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="E19" s="157" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="F19" s="158">
         <v>185000</v>
       </c>
       <c r="G19" s="159" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="H19" s="47" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22550,22 +22687,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="F20" s="65">
         <v>126500</v>
       </c>
       <c r="G20" s="135" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="H20" s="47" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22573,19 +22710,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="F21" s="65">
         <v>30000</v>
       </c>
       <c r="G21" s="149" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="H21" s="48"/>
     </row>
@@ -22594,22 +22731,22 @@
         <v>20</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="F22" s="65">
         <v>44000</v>
       </c>
       <c r="G22" s="135" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="H22" s="47" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22617,20 +22754,20 @@
         <v>21</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="E23" s="114" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="F23" s="65">
         <v>376000</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="47" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -22741,7 +22878,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -22753,7 +22890,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -22770,29 +22907,29 @@
       <c r="H2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E3" s="100" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F3" s="79">
         <v>205000</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="H3" s="62"/>
     </row>
@@ -22801,19 +22938,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F4" s="65">
         <v>130000</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="H4" s="60"/>
     </row>
@@ -22822,19 +22959,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E5" s="101" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F5" s="53">
         <v>350000</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -22843,19 +22980,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F6" s="54">
         <v>35000</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -22867,16 +23004,16 @@
         <v>81</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F7" s="54">
         <v>40000</v>
       </c>
       <c r="G7" s="112" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -22885,7 +23022,7 @@
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
       <c r="E8" s="104" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="F8" s="54"/>
       <c r="G8" s="24"/>
@@ -23112,20 +23249,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>608</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>601</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="58"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -23142,10 +23279,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="179" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="179"/>
+      <c r="K2" s="178" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="178"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -23160,10 +23297,10 @@
         <v>405000</v>
       </c>
       <c r="G3" s="108" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L3" s="84">
         <v>50000</v>
@@ -23177,22 +23314,22 @@
         <v>41</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F4" s="54">
         <v>50000</v>
       </c>
       <c r="G4" s="103" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H4" s="25" t="s">
         <v>19</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L4" s="84">
         <v>100000</v>
@@ -23206,7 +23343,7 @@
         <v>81</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E5" s="49" t="s">
         <v>49</v>
@@ -23215,13 +23352,13 @@
         <v>200000</v>
       </c>
       <c r="G5" s="103" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H5" s="85" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L5" s="84">
         <v>200000</v>
@@ -23235,20 +23372,20 @@
         <v>73</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F6" s="54">
         <v>50000</v>
       </c>
       <c r="G6" s="103" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="82" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L6" s="84">
         <v>20000</v>
@@ -23259,23 +23396,23 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F7" s="54">
         <v>50000</v>
       </c>
       <c r="G7" s="103" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H7" s="25"/>
       <c r="K7" s="82" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L7" s="84">
         <v>30000</v>
@@ -23289,22 +23426,22 @@
         <v>71</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="F8" s="54">
         <v>220000</v>
       </c>
-      <c r="G8" s="180" t="s">
-        <v>684</v>
+      <c r="G8" s="179" t="s">
+        <v>676</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K8" s="82" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L8" s="84">
         <v>20000</v>
@@ -23315,10 +23452,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E9" s="45" t="s">
         <v>78</v>
@@ -23326,12 +23463,12 @@
       <c r="F9" s="54">
         <v>100000</v>
       </c>
-      <c r="G9" s="181"/>
+      <c r="G9" s="180"/>
       <c r="H9" s="25" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L9" s="84">
         <v>270000</v>
@@ -23342,22 +23479,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F10" s="54">
         <v>40000</v>
       </c>
       <c r="G10" s="103" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23371,13 +23508,13 @@
         <v>20254.400000000001</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="F11" s="54">
         <v>40000</v>
       </c>
       <c r="G11" s="103" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="H11" s="25"/>
     </row>
@@ -23389,7 +23526,7 @@
         <v>73</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>1</v>
@@ -23398,7 +23535,7 @@
         <v>515000</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="H12" s="25"/>
     </row>
@@ -23410,16 +23547,16 @@
         <v>51</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="F13" s="53">
         <v>50000</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="H13" s="25"/>
     </row>
@@ -23428,19 +23565,19 @@
         <v>12</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F14" s="53">
         <v>20000</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H14" s="25"/>
     </row>
@@ -23452,16 +23589,16 @@
         <v>70</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F15" s="53">
         <v>50000</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="H15" s="25"/>
     </row>
@@ -23473,7 +23610,7 @@
         <v>41</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E16" s="45" t="s">
         <v>0</v>
@@ -23482,7 +23619,7 @@
         <v>330000</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H16" s="25"/>
     </row>
@@ -23491,19 +23628,19 @@
         <v>15</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="F17" s="53">
         <v>55000</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H17" s="25"/>
     </row>
@@ -23515,7 +23652,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="E18" s="45" t="s">
         <v>14</v>
@@ -23524,7 +23661,7 @@
         <v>50000</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H18" s="25"/>
     </row>
@@ -23536,16 +23673,16 @@
         <v>51</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F19" s="53">
         <v>66000</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="H19" s="25"/>
     </row>
@@ -23554,19 +23691,19 @@
         <v>18</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F20" s="53">
         <v>132000</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="H20" s="25"/>
     </row>
@@ -23575,19 +23712,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F21" s="53">
         <v>44000</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="H21" s="25"/>
     </row>
@@ -23596,22 +23733,22 @@
         <v>20</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="F22" s="65">
         <v>39600</v>
       </c>
       <c r="G22" s="172" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23619,37 +23756,37 @@
         <v>21</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F23" s="65">
         <v>29700</v>
       </c>
-      <c r="G23" s="183"/>
+      <c r="G23" s="182"/>
     </row>
     <row r="24" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="12">
         <v>22</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="F24" s="65">
         <v>165000</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23657,19 +23794,19 @@
         <v>23</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>766</v>
-      </c>
-      <c r="F25" s="182">
+        <v>758</v>
+      </c>
+      <c r="F25" s="181">
         <v>60500</v>
       </c>
       <c r="G25" s="172" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23677,15 +23814,15 @@
         <v>24</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>767</v>
-      </c>
-      <c r="F26" s="182"/>
+        <v>759</v>
+      </c>
+      <c r="F26" s="181"/>
       <c r="G26" s="173"/>
     </row>
     <row r="27" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23693,22 +23830,22 @@
         <v>25</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="F27" s="65">
         <v>84600</v>
       </c>
       <c r="G27" s="135" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23716,16 +23853,16 @@
         <v>25</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="F28" s="65">
         <v>134000</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23733,19 +23870,19 @@
         <v>26</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="F29" s="65">
         <v>30000</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -23812,7 +23949,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -23824,7 +23961,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -23847,19 +23984,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="F3" s="22">
         <v>220000</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H3" s="62"/>
     </row>
@@ -24140,7 +24277,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -24152,7 +24289,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -24175,17 +24312,17 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F3" s="2">
         <v>95000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H3" s="10"/>
     </row>
@@ -24194,19 +24331,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F4" s="22">
         <v>150000</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -24215,19 +24352,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="F5" s="53">
         <v>100000</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -24490,7 +24627,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -24502,7 +24639,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -24525,22 +24662,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F3" s="2">
         <v>95000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -24548,19 +24685,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="F4" s="22">
         <v>60000</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -24569,19 +24706,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F5" s="53">
         <v>80000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -24590,19 +24727,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D6" s="24">
         <v>2025.7</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F6" s="54">
         <v>70000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -24611,19 +24748,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F7" s="54">
         <v>80000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -24632,19 +24769,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="F8" s="54">
         <v>600000</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -24654,16 +24791,16 @@
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="24" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="F9" s="54">
         <v>125400</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -24672,22 +24809,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="F10" s="54">
         <v>70000</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -24695,13 +24832,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F11" s="54">
         <v>148500</v>
@@ -24914,7 +25051,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -24926,7 +25063,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -24949,19 +25086,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E3" s="113" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="F3" s="64">
         <v>300000</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="H3" s="10"/>
     </row>
@@ -24970,19 +25107,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="F4" s="2">
         <v>300000</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -25254,7 +25391,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -25266,7 +25403,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -25583,10 +25720,10 @@
         <v>61</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="G1" s="32" t="s">
         <v>26</v>
@@ -25611,13 +25748,13 @@
       <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="214" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="215" t="s">
+      <c r="D2" s="214" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="215" t="s">
+      <c r="E2" s="214" t="s">
         <v>66</v>
       </c>
       <c r="F2" s="20" t="s">
@@ -25635,16 +25772,16 @@
         <v>28</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
       <c r="F3" s="20" t="s">
         <v>81</v>
       </c>
@@ -25660,16 +25797,16 @@
         <v>28</v>
       </c>
       <c r="L3" s="26" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10">
         <v>3</v>
       </c>
-      <c r="C4" s="215"/>
-      <c r="D4" s="215"/>
-      <c r="E4" s="215"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
       <c r="F4" s="35" t="s">
         <v>70</v>
       </c>
@@ -25684,48 +25821,48 @@
         <v>425000</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>4</v>
       </c>
-      <c r="C5" s="215"/>
-      <c r="D5" s="215"/>
-      <c r="E5" s="215"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="214"/>
+      <c r="E5" s="214"/>
       <c r="F5" s="20" t="s">
         <v>83</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J5" s="22">
         <v>400000</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
         <v>5</v>
       </c>
-      <c r="C6" s="215"/>
-      <c r="D6" s="215"/>
-      <c r="E6" s="215"/>
+      <c r="C6" s="214"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="214"/>
       <c r="F6" s="35" t="s">
         <v>62</v>
       </c>
@@ -25738,7 +25875,7 @@
         <v>420000</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L6" s="34"/>
     </row>
@@ -25746,9 +25883,9 @@
       <c r="B7" s="10">
         <v>6</v>
       </c>
-      <c r="C7" s="215"/>
-      <c r="D7" s="215"/>
-      <c r="E7" s="215"/>
+      <c r="C7" s="214"/>
+      <c r="D7" s="214"/>
+      <c r="E7" s="214"/>
       <c r="F7" s="24" t="s">
         <v>65</v>
       </c>
@@ -25757,33 +25894,33 @@
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="J7" s="38">
         <v>300000</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="L7" s="40" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="M7" s="29"/>
     </row>
     <row r="8" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="216" t="s">
-        <v>578</v>
-      </c>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
+      <c r="B8" s="215" t="s">
+        <v>571</v>
+      </c>
+      <c r="C8" s="215"/>
+      <c r="D8" s="215"/>
+      <c r="E8" s="215"/>
+      <c r="F8" s="215"/>
+      <c r="G8" s="215"/>
+      <c r="H8" s="215"/>
+      <c r="I8" s="215"/>
+      <c r="J8" s="215"/>
+      <c r="K8" s="215"/>
+      <c r="L8" s="215"/>
       <c r="M8" s="29"/>
     </row>
     <row r="9" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -26236,7 +26373,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -26248,7 +26385,7 @@
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -26274,16 +26411,16 @@
         <v>70</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F3" s="2">
         <v>225000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="H3" s="10"/>
     </row>
@@ -26295,16 +26432,16 @@
         <v>70</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="F4" s="22">
         <v>235000</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -26316,16 +26453,16 @@
         <v>70</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F5" s="53">
         <v>20000</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -26334,19 +26471,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="F6" s="54">
         <v>115000</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -26359,13 +26496,13 @@
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="45" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F7" s="54">
         <v>50000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -26374,17 +26511,17 @@
         <v>5</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="46" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="F8" s="54">
         <v>165000</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -26393,19 +26530,19 @@
         <v>6</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="F9" s="54">
         <v>368500</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -26414,19 +26551,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="F10" s="54">
         <v>44000</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="H10" s="25"/>
       <c r="L10">
@@ -26438,19 +26575,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="F11" s="54">
         <v>44000</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="H11" s="25"/>
       <c r="L11">
@@ -26680,7 +26817,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -26692,7 +26829,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -26715,19 +26852,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F3" s="2">
         <v>45000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="H3" s="10"/>
     </row>
@@ -27008,22 +27145,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="129"/>
-      <c r="B1" s="217" t="s">
-        <v>714</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>706</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="129"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="129"/>
       <c r="B2" s="129"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -27048,20 +27185,20 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="8" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="F3" s="2">
         <v>45000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I3" s="129"/>
     </row>
@@ -27071,20 +27208,20 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="49" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="F4" s="22">
         <v>700000</v>
       </c>
-      <c r="G4" s="193" t="s">
-        <v>884</v>
-      </c>
-      <c r="H4" s="219" t="s">
-        <v>886</v>
+      <c r="G4" s="192" t="s">
+        <v>876</v>
+      </c>
+      <c r="H4" s="218" t="s">
+        <v>878</v>
       </c>
       <c r="I4" s="129"/>
     </row>
@@ -27094,19 +27231,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="D5" s="21">
         <v>26</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="F5" s="53">
         <v>258500</v>
       </c>
-      <c r="G5" s="195"/>
-      <c r="H5" s="220"/>
+      <c r="G5" s="194"/>
+      <c r="H5" s="219"/>
       <c r="I5" s="129"/>
     </row>
     <row r="6" spans="1:9" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -28359,22 +28496,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="134"/>
-      <c r="B1" s="217" t="s">
-        <v>782</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>774</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="134"/>
       <c r="B2" s="134"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -28399,7 +28536,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="8"/>
@@ -28413,7 +28550,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="49"/>
@@ -28428,13 +28565,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="F5" s="54">
         <v>350000</v>
@@ -28449,11 +28586,11 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="46" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="23"/>
@@ -28466,11 +28603,11 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="45" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="F7" s="54">
         <v>30000</v>
@@ -29620,7 +29757,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="167" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="167"/>
       <c r="D1" s="167"/>
@@ -29632,7 +29769,7 @@
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="29"/>
       <c r="C2" s="32" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>86</v>
@@ -29655,22 +29792,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="F3" s="2">
         <v>200000</v>
       </c>
       <c r="G3" s="108" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -29678,19 +29815,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F4" s="42">
         <v>220000</v>
       </c>
       <c r="G4" s="103" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="H4" s="25"/>
     </row>
@@ -29699,19 +29836,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="F5" s="53">
         <v>800000</v>
       </c>
       <c r="G5" s="102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -29720,10 +29857,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>7</v>
@@ -29732,7 +29869,7 @@
         <v>790000</v>
       </c>
       <c r="G6" s="102" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -29741,19 +29878,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>680</v>
-      </c>
-      <c r="F7" s="184">
+        <v>672</v>
+      </c>
+      <c r="F7" s="183">
         <v>845000</v>
       </c>
-      <c r="G7" s="186" t="s">
-        <v>368</v>
+      <c r="G7" s="185" t="s">
+        <v>366</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -29762,16 +29899,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>572</v>
-      </c>
-      <c r="F8" s="185"/>
-      <c r="G8" s="187"/>
+        <v>565</v>
+      </c>
+      <c r="F8" s="184"/>
+      <c r="G8" s="186"/>
       <c r="H8" s="25"/>
     </row>
     <row r="9" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -29945,22 +30082,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="134"/>
-      <c r="B1" s="217" t="s">
-        <v>819</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>811</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="134"/>
       <c r="B2" s="134"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -29985,19 +30122,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="F3" s="2">
         <v>140000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="I3" s="134"/>
     </row>
@@ -31186,22 +31323,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="134"/>
-      <c r="B1" s="217" t="s">
-        <v>914</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>906</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="134"/>
       <c r="B2" s="134"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -31226,19 +31363,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="F3" s="2">
         <v>150000</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="I3" s="134"/>
     </row>
@@ -32427,22 +32564,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="134"/>
-      <c r="B1" s="217" t="s">
-        <v>925</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>917</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="134"/>
       <c r="B2" s="134"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -32469,7 +32606,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="8" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="F3" s="2">
         <v>944000</v>
@@ -33662,22 +33799,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="134"/>
-      <c r="B1" s="217" t="s">
-        <v>974</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>966</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="134"/>
       <c r="B2" s="134"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -33702,13 +33839,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="F3" s="2">
         <v>95000</v>
@@ -34901,22 +35038,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="134"/>
-      <c r="B1" s="217" t="s">
-        <v>977</v>
-      </c>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
+      <c r="B1" s="216" t="s">
+        <v>969</v>
+      </c>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
       <c r="I1" s="134"/>
     </row>
     <row r="2" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="134"/>
       <c r="B2" s="134"/>
       <c r="C2" s="130" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="130" t="s">
         <v>86</v>
@@ -36125,7 +36262,7 @@
   <sheetData>
     <row r="4" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="D4" s="65">
         <v>55000</v>
@@ -36136,7 +36273,7 @@
     </row>
     <row r="5" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="10" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="D5" s="65">
         <v>11000</v>
@@ -36147,7 +36284,7 @@
     </row>
     <row r="6" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="10" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="D6" s="65">
         <v>55000</v>
@@ -36158,7 +36295,7 @@
     </row>
     <row r="7" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="10" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="D7" s="65">
         <v>33000</v>
@@ -36169,7 +36306,7 @@
     </row>
     <row r="8" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="10" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="D8" s="65">
         <v>26400</v>
@@ -36180,7 +36317,7 @@
     </row>
     <row r="9" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="10" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="D9" s="65">
         <v>44000</v>
@@ -36191,7 +36328,7 @@
     </row>
     <row r="10" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="10" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D10" s="65">
         <v>66000</v>
@@ -36202,7 +36339,7 @@
     </row>
     <row r="11" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="10" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="D11" s="65">
         <v>55000</v>
@@ -36213,7 +36350,7 @@
     </row>
     <row r="12" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="10" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="D12" s="65">
         <v>33000</v>
@@ -36224,7 +36361,7 @@
     </row>
     <row r="13" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="10" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="D13" s="65">
         <v>44000</v>
@@ -36235,7 +36372,7 @@
     </row>
     <row r="14" spans="3:5" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="10" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D14" s="65">
         <v>363000</v>
@@ -36281,20 +36418,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>544</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>537</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -36325,7 +36462,7 @@
         <v>300000</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H3" s="62"/>
     </row>
@@ -36337,16 +36474,16 @@
         <v>51</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="F4" s="42">
         <v>150000</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="H4" s="60"/>
     </row>
@@ -36361,13 +36498,13 @@
         <v>2024</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F5" s="53">
         <v>390000</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -36379,16 +36516,16 @@
         <v>83</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F6" s="54">
         <v>300000</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -36400,16 +36537,16 @@
         <v>60</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F7" s="54">
         <v>300000</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -36418,17 +36555,17 @@
         <v>6</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="46" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F8" s="54">
         <v>35000</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -36437,19 +36574,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="F9" s="54">
         <v>350000</v>
       </c>
       <c r="G9" s="128" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="H9" s="25"/>
     </row>
@@ -36458,19 +36595,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="F10" s="54">
         <v>82500</v>
       </c>
-      <c r="G10" s="188" t="s">
-        <v>788</v>
+      <c r="G10" s="187" t="s">
+        <v>780</v>
       </c>
       <c r="H10" s="25"/>
     </row>
@@ -36479,18 +36616,18 @@
         <v>9</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="F11" s="54">
         <v>44000</v>
       </c>
-      <c r="G11" s="183"/>
+      <c r="G11" s="182"/>
       <c r="H11" s="25"/>
     </row>
     <row r="12" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -37820,20 +37957,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>392</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -37859,16 +37996,16 @@
         <v>60</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F3" s="64">
         <v>200000</v>
       </c>
-      <c r="G3" s="189" t="s">
-        <v>808</v>
+      <c r="G3" s="188" t="s">
+        <v>800</v>
       </c>
       <c r="H3" s="62"/>
     </row>
@@ -37880,15 +38017,15 @@
         <v>51</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="F4" s="42">
         <v>100000</v>
       </c>
-      <c r="G4" s="190"/>
+      <c r="G4" s="189"/>
       <c r="H4" s="60"/>
     </row>
     <row r="5" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -37896,17 +38033,17 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>791</v>
-      </c>
-      <c r="D5" s="196" t="s">
-        <v>806</v>
+        <v>783</v>
+      </c>
+      <c r="D5" s="195" t="s">
+        <v>798</v>
       </c>
       <c r="E5" s="49"/>
-      <c r="F5" s="191">
+      <c r="F5" s="190">
         <v>900000</v>
       </c>
-      <c r="G5" s="193" t="s">
-        <v>809</v>
+      <c r="G5" s="192" t="s">
+        <v>801</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -37915,12 +38052,12 @@
         <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>792</v>
-      </c>
-      <c r="D6" s="197"/>
+        <v>784</v>
+      </c>
+      <c r="D6" s="196"/>
       <c r="E6" s="46"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="194"/>
+      <c r="F6" s="181"/>
+      <c r="G6" s="193"/>
       <c r="H6" s="25"/>
     </row>
     <row r="7" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -37928,12 +38065,12 @@
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>793</v>
-      </c>
-      <c r="D7" s="198"/>
+        <v>785</v>
+      </c>
+      <c r="D7" s="197"/>
       <c r="E7" s="45"/>
-      <c r="F7" s="192"/>
-      <c r="G7" s="195"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="194"/>
       <c r="H7" s="25"/>
     </row>
     <row r="8" spans="2:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -37941,13 +38078,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="F8" s="54">
         <v>64000</v>
@@ -39316,20 +39453,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>383</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="109"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -39346,10 +39483,10 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="179" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="179"/>
+      <c r="K2" s="178" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="178"/>
     </row>
     <row r="3" spans="2:13" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
@@ -39362,17 +39499,17 @@
         <v>2024.9</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="F3" s="64">
         <v>240000</v>
       </c>
-      <c r="G3" s="194" t="s">
-        <v>425</v>
+      <c r="G3" s="193" t="s">
+        <v>422</v>
       </c>
       <c r="H3" s="62"/>
       <c r="K3" s="82" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L3" s="84">
         <v>100000</v>
@@ -39390,15 +39527,15 @@
         <v>2024.9</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F4" s="42">
         <v>520000</v>
       </c>
-      <c r="G4" s="194"/>
+      <c r="G4" s="193"/>
       <c r="H4" s="60"/>
       <c r="K4" s="82" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L4" s="84">
         <v>30000</v>
@@ -39415,15 +39552,15 @@
         <v>2024.9</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F5" s="53">
         <v>265000</v>
       </c>
-      <c r="G5" s="202"/>
+      <c r="G5" s="201"/>
       <c r="H5" s="25"/>
       <c r="K5" s="82" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L5" s="84">
         <v>40000</v>
@@ -39434,7 +39571,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="46" t="s">
@@ -39443,12 +39580,12 @@
       <c r="F6" s="54">
         <v>165000</v>
       </c>
-      <c r="G6" s="203" t="s">
-        <v>689</v>
+      <c r="G6" s="202" t="s">
+        <v>681</v>
       </c>
       <c r="H6" s="25"/>
       <c r="K6" s="82" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L6" s="84">
         <v>30000</v>
@@ -39463,17 +39600,17 @@
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="45" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="F7" s="54">
         <v>335000</v>
       </c>
-      <c r="G7" s="204"/>
+      <c r="G7" s="203"/>
       <c r="H7" s="25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K7" s="82" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L7" s="84">
         <v>150000</v>
@@ -39488,15 +39625,15 @@
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="46" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F8" s="54">
         <v>30000</v>
       </c>
-      <c r="G8" s="205"/>
+      <c r="G8" s="204"/>
       <c r="H8" s="25"/>
       <c r="K8" s="82" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L8" s="84">
         <v>100000</v>
@@ -39511,17 +39648,17 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="45" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="F9" s="54">
         <v>100000</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H9" s="25"/>
       <c r="K9" s="82" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L9" s="84">
         <v>40000</v>
@@ -39536,17 +39673,17 @@
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="H10" s="25"/>
       <c r="K10" s="82" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L10" s="84">
         <v>30000</v>
@@ -39557,23 +39694,23 @@
         <v>9</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="F11" s="54">
         <v>200000</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H11" s="25"/>
       <c r="K11" s="82" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L11" s="84">
         <v>15000</v>
@@ -39584,20 +39721,20 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="45" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="F12" s="53">
         <v>350000</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="K12" s="82" t="s">
         <v>90</v>
@@ -39611,19 +39748,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F13" s="53">
         <v>490000</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="H13" s="25"/>
       <c r="K13" s="82" t="s">
@@ -39641,22 +39778,22 @@
         <v>65</v>
       </c>
       <c r="D14" s="117" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E14" s="118" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="F14" s="119">
         <v>150000</v>
       </c>
-      <c r="G14" s="206" t="s">
-        <v>506</v>
-      </c>
-      <c r="H14" s="207" t="s">
-        <v>686</v>
+      <c r="G14" s="205" t="s">
+        <v>499</v>
+      </c>
+      <c r="H14" s="206" t="s">
+        <v>678</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L14" s="84">
         <v>50000</v>
@@ -39667,21 +39804,21 @@
         <v>13</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D15" s="117" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E15" s="118" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="F15" s="119">
         <v>85000</v>
       </c>
-      <c r="G15" s="206"/>
-      <c r="H15" s="208"/>
+      <c r="G15" s="205"/>
+      <c r="H15" s="207"/>
       <c r="K15" s="82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L15" s="84">
         <v>30000</v>
@@ -39695,20 +39832,20 @@
         <v>51</v>
       </c>
       <c r="D16" s="117" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E16" s="118" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="F16" s="119">
         <v>50000</v>
       </c>
       <c r="G16" s="120" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="H16" s="121"/>
       <c r="K16" s="82" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L16" s="84">
         <v>20000</v>
@@ -39722,7 +39859,7 @@
         <v>79</v>
       </c>
       <c r="D17" s="117" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="E17" s="118" t="s">
         <v>13</v>
@@ -39731,11 +39868,11 @@
         <v>126500</v>
       </c>
       <c r="G17" s="120" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="H17" s="121"/>
       <c r="K17" s="82" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L17" s="84">
         <v>35000</v>
@@ -39750,19 +39887,19 @@
       </c>
       <c r="D18" s="117"/>
       <c r="E18" s="122" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="F18" s="119">
         <v>550000</v>
       </c>
       <c r="G18" s="120" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="H18" s="121" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="K18" s="82" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L18" s="84">
         <v>70000</v>
@@ -39773,23 +39910,23 @@
         <v>17</v>
       </c>
       <c r="C19" s="117" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D19" s="117"/>
       <c r="E19" s="118" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="F19" s="119">
         <v>60000</v>
       </c>
-      <c r="G19" s="199" t="s">
-        <v>711</v>
+      <c r="G19" s="198" t="s">
+        <v>703</v>
       </c>
       <c r="H19" s="121" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K19" s="82" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="L19" s="84">
         <v>80000</v>
@@ -39804,17 +39941,17 @@
       </c>
       <c r="D20" s="117"/>
       <c r="E20" s="118" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="F20" s="119">
         <v>60000</v>
       </c>
-      <c r="G20" s="201"/>
+      <c r="G20" s="200"/>
       <c r="H20" s="121" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K20" s="82" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L20" s="84">
         <v>60000</v>
@@ -39825,19 +39962,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="139" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="D21" s="139" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="E21" s="144" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="F21" s="141">
         <v>735000</v>
       </c>
-      <c r="G21" s="199" t="s">
-        <v>918</v>
+      <c r="G21" s="198" t="s">
+        <v>910</v>
       </c>
       <c r="H21" s="143"/>
     </row>
@@ -39846,20 +39983,20 @@
         <v>20</v>
       </c>
       <c r="C22" s="139" t="s">
+        <v>841</v>
+      </c>
+      <c r="D22" s="139" t="s">
         <v>849</v>
       </c>
-      <c r="D22" s="139" t="s">
-        <v>857</v>
-      </c>
       <c r="E22" s="140" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="F22" s="141">
         <v>340000</v>
       </c>
-      <c r="G22" s="200"/>
+      <c r="G22" s="199"/>
       <c r="H22" s="143" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -39867,20 +40004,20 @@
         <v>21</v>
       </c>
       <c r="C23" s="139" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="D23" s="139" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="E23" s="140" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="F23" s="141">
         <v>100000</v>
       </c>
-      <c r="G23" s="201"/>
+      <c r="G23" s="200"/>
       <c r="H23" s="143" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -39888,13 +40025,13 @@
         <v>22</v>
       </c>
       <c r="C24" s="139" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="D24" s="139" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="E24" s="140" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="F24" s="141">
         <v>44000</v>
@@ -39907,22 +40044,22 @@
         <v>23</v>
       </c>
       <c r="C25" s="139" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="D25" s="139" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="E25" s="147" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="F25" s="141">
         <v>760000</v>
       </c>
       <c r="G25" s="151" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="H25" s="143" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -41144,20 +41281,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>386</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>384</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -41174,29 +41311,29 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="210"/>
+      <c r="K2" s="209" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="209"/>
     </row>
     <row r="3" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>1</v>
       </c>
-      <c r="C3" s="197" t="s">
+      <c r="C3" s="196" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F3" s="64">
         <v>300000</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H3" s="62"/>
     </row>
@@ -41204,18 +41341,18 @@
       <c r="B4" s="24">
         <v>2</v>
       </c>
-      <c r="C4" s="209"/>
+      <c r="C4" s="208"/>
       <c r="D4" s="12" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F4" s="42">
         <v>40000</v>
       </c>
       <c r="G4" s="74" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H4" s="60"/>
     </row>
@@ -41224,10 +41361,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E5" s="68" t="s">
         <v>34</v>
@@ -41236,10 +41373,10 @@
         <v>250000</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="34.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -41247,19 +41384,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F6" s="54">
         <v>42000</v>
       </c>
       <c r="G6" s="76" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H6" s="25"/>
     </row>
@@ -41271,16 +41408,16 @@
         <v>62</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="F7" s="54">
         <v>77000</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -42651,20 +42788,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="178" t="s">
-        <v>705</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
+      <c r="B1" s="177" t="s">
+        <v>697</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>86</v>
@@ -42681,33 +42818,33 @@
       <c r="H2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="179" t="s">
-        <v>663</v>
-      </c>
-      <c r="L2" s="179"/>
+      <c r="K2" s="178" t="s">
+        <v>655</v>
+      </c>
+      <c r="L2" s="178"/>
     </row>
     <row r="3" spans="2:12" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F3" s="64">
         <v>450000</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="H3" s="62"/>
       <c r="K3" s="82" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L3" s="84">
         <v>15000</v>
@@ -42724,17 +42861,17 @@
         <v>2025.2</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F4" s="42">
         <v>164000</v>
       </c>
       <c r="G4" s="88" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="H4" s="60"/>
       <c r="K4" s="82" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L4" s="84">
         <v>40000</v>
@@ -42748,14 +42885,14 @@
         <v>79</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E5" s="68"/>
       <c r="F5" s="53">
         <v>490000</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="H5" s="25"/>
     </row>
@@ -42767,10 +42904,10 @@
         <v>60</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="71"/>
@@ -42781,10 +42918,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E7" s="45" t="s">
         <v>33</v>
@@ -42793,7 +42930,7 @@
         <v>85000</v>
       </c>
       <c r="G7" s="88" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="H7" s="25"/>
     </row>
@@ -42805,16 +42942,16 @@
         <v>62</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="F8" s="54">
         <v>65000</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H8" s="25"/>
     </row>
@@ -42826,10 +42963,10 @@
         <v>60</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="F9" s="54">
         <v>572000</v>
@@ -42844,19 +42981,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="136" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="F10" s="54">
         <v>79400</v>
       </c>
       <c r="G10" s="88" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="H10" s="25"/>
     </row>
@@ -42865,19 +43002,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="F11" s="54">
         <v>89100</v>
       </c>
       <c r="G11" s="88" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="H11" s="25"/>
     </row>
@@ -42886,19 +43023,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="F12" s="53">
         <v>90000</v>
       </c>
       <c r="G12" s="88" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="H12" s="25"/>
     </row>
